--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>45978.5625</v>
+        <v>45978.375</v>
       </c>
     </row>
     <row r="3">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45978.6875</v>
+        <v>45978.5625</v>
       </c>
     </row>
     <row r="4">
@@ -1085,6 +1085,125 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
+        <v>45978.6875</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Foggia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Cavese</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
       </c>
     </row>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45978.5625</v>
+        <v>45978.375</v>
       </c>
     </row>
     <row r="4">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45978.6875</v>
+        <v>45978.5625</v>
       </c>
     </row>
     <row r="5">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1204,6 +1204,125 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
+        <v>45978.6875</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Spain Segunda División</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cultural y Deportiva Leonesa</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Málaga CF</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
       </c>
     </row>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45978.5625</v>
+        <v>45978.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45978.6875</v>
+        <v>45978.5625</v>
       </c>
     </row>
     <row r="6">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,111 +1218,230 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pergolettese</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Giana Erminio</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
+        <v>45978.6875</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Spain Segunda División</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Málaga CF</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>2.22</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M8" t="n">
         <v>3.28</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N8" t="n">
         <v>3.17</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2.12</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AB8" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="3" t="n">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>45978.6875</v>
       </c>
     </row>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="M7" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>3.17</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
         <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M7" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
         <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>3.17</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="M8" t="n">
         <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>3.17</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="M8" t="n">
         <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1025,40 +1025,40 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA5" t="n">
         <v>2.4</v>
@@ -1067,22 +1067,22 @@
         <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1263,40 +1263,40 @@
         <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA7" t="n">
         <v>2.18</v>
@@ -1305,22 +1305,22 @@
         <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1025,7 +1025,7 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="P5" t="n">
         <v>1.95</v>
@@ -1070,7 +1070,7 @@
         <v>4.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE5" t="n">
         <v>2.02</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P6" t="n">
         <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1025,19 +1025,19 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T5" t="n">
         <v>3.5</v>
@@ -1046,10 +1046,10 @@
         <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1067,7 +1067,7 @@
         <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
@@ -1079,10 +1079,10 @@
         <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.58</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1263,31 +1263,31 @@
         <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="T7" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="U7" t="n">
         <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1.04</v>
@@ -1311,16 +1311,16 @@
         <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.46</v>
+        <v>3.12</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -856,7 +856,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45978.54166666666</v>
+        <v>45978.5</v>
       </c>
     </row>
     <row r="5">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="T6" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.01</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.58</v>
+        <v>3.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
         <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>3.16</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.67</v>
+        <v>3.65</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>3.09</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.12</v>
+        <v>2.59</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1028,16 +1028,16 @@
         <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
         <v>3.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
         <v>3.5</v>
@@ -1055,10 +1055,10 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AA5" t="n">
         <v>2.4</v>
@@ -1067,7 +1067,7 @@
         <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.12</v>
+        <v>2.59</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1263,7 +1263,7 @@
         <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="P7" t="n">
         <v>1.98</v>
@@ -1296,7 +1296,7 @@
         <v>1.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AA7" t="n">
         <v>2.03</v>
@@ -1320,7 +1320,7 @@
         <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>3.17</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="T8" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.61</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="O5" t="n">
         <v>3.5</v>
@@ -1034,7 +1034,7 @@
         <v>3.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
         <v>2.36</v>
@@ -1061,10 +1061,10 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC5" t="n">
         <v>4.75</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.35</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.65</v>
+        <v>2.67</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="T7" t="n">
-        <v>3.34</v>
+        <v>3.09</v>
       </c>
       <c r="U7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.25</v>
-      </c>
-      <c r="V7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
         <v>3.48</v>
@@ -1394,7 +1394,7 @@
         <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
@@ -1421,7 +1421,7 @@
         <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
         <v>3.85</v>
@@ -1436,10 +1436,10 @@
         <v>1.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>3.5</v>
@@ -1031,7 +1031,7 @@
         <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.41</v>
+        <v>3.62</v>
       </c>
       <c r="R5" t="n">
         <v>1.54</v>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1061,10 +1061,10 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>4.75</v>
@@ -1076,13 +1076,13 @@
         <v>2.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG5" t="n">
         <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1135,28 +1135,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.74</v>
+        <v>3.93</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="T6" t="n">
         <v>3.5</v>
@@ -1171,28 +1171,28 @@
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
         <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AF6" t="n">
         <v>1.63</v>
@@ -1254,70 +1254,70 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O7" t="n">
         <v>3.4</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.67</v>
+        <v>2.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="T7" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V7" t="n">
         <v>9.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
         <v>2.59</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="n">
         <v>1.25</v>
@@ -1379,67 +1379,67 @@
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="P8" t="n">
         <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
         <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.02</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
         <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1025,13 +1025,13 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
         <v>1.54</v>
@@ -1040,10 +1040,10 @@
         <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V5" t="n">
         <v>10</v>
@@ -1055,7 +1055,7 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
         <v>2.46</v>
@@ -1076,7 +1076,7 @@
         <v>2.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
         <v>1.37</v>
@@ -1144,40 +1144,40 @@
         <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AA6" t="n">
         <v>2.03</v>
@@ -1186,16 +1186,16 @@
         <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
         <v>1.32</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>3.17</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U7" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V7" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>2.99</v>
+        <v>4.16</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.15</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.58</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AF6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.43</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M7" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.71</v>
+        <v>4.16</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
         <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4.16</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
         <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1025,25 +1025,25 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
         <v>2.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
         <v>10</v>
@@ -1055,7 +1055,7 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z5" t="n">
         <v>2.46</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>2.71</v>
+        <v>3.98</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
         <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>4.16</v>
+        <v>3.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.86</v>
+        <v>3.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="O8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.15</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.58</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>4.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.11</v>
+        <v>1.86</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
         <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
         <v>2.36</v>
@@ -1061,10 +1061,10 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AC5" t="n">
         <v>4.75</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.95</v>
+        <v>2.37</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3.98</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.84</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.36</v>
+        <v>3.98</v>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.98</v>
+        <v>2.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="R8" t="n">
         <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AA8" t="n">
         <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
         <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="M6" t="n">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.98</v>
+        <v>2.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.54</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>2.86</v>
       </c>
       <c r="O7" t="n">
-        <v>3.98</v>
+        <v>3.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>8.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1385,7 +1385,7 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
         <v>3.85</v>
@@ -1403,10 +1403,10 @@
         <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
@@ -1421,7 +1421,7 @@
         <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
         <v>4.23</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
         <v>3.5</v>
@@ -1061,10 +1061,10 @@
         <v>2.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>4.75</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.23</v>
+        <v>2.48</v>
       </c>
       <c r="M6" t="n">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="O7" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>4.23</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>3.23</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.85</v>
+        <v>2.81</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.23</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
         <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45978.375</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45978.375</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1031,10 +1031,10 @@
         <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
         <v>2.36</v>
@@ -1046,7 +1046,7 @@
         <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1055,10 +1055,10 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AA5" t="n">
         <v>2.4</v>
@@ -1067,7 +1067,7 @@
         <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
@@ -1079,10 +1079,10 @@
         <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="N6" t="n">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="O6" t="n">
-        <v>3.36</v>
+        <v>2.71</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>2.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>5</v>
+        <v>4.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.22</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>3.58</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.76</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.23</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1382,40 +1382,40 @@
         <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="P8" t="n">
         <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
         <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA8" t="n">
         <v>2.18</v>
@@ -1424,22 +1424,22 @@
         <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>3.71</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>4.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
         <v>3.2</v>
@@ -689,43 +689,43 @@
         <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45978.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.94</v>
       </c>
-      <c r="M3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
       <c r="Q3" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45978.375</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M4" t="n">
         <v>3.15</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>1.82</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45978.5</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
         <v>3.5</v>
@@ -1049,7 +1049,7 @@
         <v>8.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1061,10 +1061,10 @@
         <v>2.49</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC5" t="n">
         <v>4.73</v>
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
         <v>3.85</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
         <v>8.800000000000001</v>
@@ -1171,19 +1171,19 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
         <v>4.23</v>
@@ -1192,16 +1192,16 @@
         <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.48</v>
+        <v>3.23</v>
       </c>
       <c r="M7" t="n">
-        <v>2.89</v>
+        <v>3.19</v>
       </c>
       <c r="N7" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>4.03</v>
       </c>
       <c r="P7" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.83</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.23</v>
+        <v>2.48</v>
       </c>
       <c r="M8" t="n">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>4.03</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>3.83</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -659,25 +659,25 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="N2" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.62</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
         <v>2.5</v>
@@ -689,13 +689,13 @@
         <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.42</v>
@@ -716,16 +716,16 @@
         <v>1.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45978.375</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD3" t="n">
         <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
         <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45978.375</v>
@@ -897,55 +897,55 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>6.22</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="U4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AC4" t="n">
         <v>5.1</v>
@@ -960,10 +960,10 @@
         <v>1.51</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45978.5</v>
@@ -1025,10 +1025,10 @@
         <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q5" t="n">
         <v>3.34</v>
@@ -1037,7 +1037,7 @@
         <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
         <v>3.5</v>
@@ -1046,43 +1046,43 @@
         <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="Z5" t="n">
         <v>2.49</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.73</v>
+        <v>5.51</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
         <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.23</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.23</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
-        <v>4.03</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.4</v>
+        <v>4.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
         <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="M8" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.83</v>
+        <v>2.83</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="T8" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -659,25 +659,25 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="O2" t="n">
         <v>2.62</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
         <v>2.5</v>
@@ -689,10 +689,10 @@
         <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.08</v>
@@ -704,10 +704,10 @@
         <v>2.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
         <v>4.3</v>
@@ -716,16 +716,16 @@
         <v>1.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45978.375</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O3" t="n">
         <v>3.2</v>
@@ -796,25 +796,25 @@
         <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
         <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
         <v>9.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.42</v>
@@ -835,7 +835,7 @@
         <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
         <v>1.75</v>
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.5</v>
+        <v>3.19</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="O4" t="n">
-        <v>6.22</v>
+        <v>5.95</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S4" t="n">
         <v>2.2</v>
@@ -927,7 +927,7 @@
         <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
@@ -936,13 +936,13 @@
         <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AB4" t="n">
         <v>1.41</v>
@@ -957,13 +957,13 @@
         <v>2.38</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45978.5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.58</v>
+        <v>2.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>2.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>5</v>
+        <v>4.29</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>3.23</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.85</v>
+        <v>2.83</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="N8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2.1</v>
       </c>
-      <c r="O8" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.43</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -1016,28 +1016,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T5" t="n">
         <v>3.5</v>
@@ -1061,28 +1061,28 @@
         <v>2.49</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
         <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>3.23</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.85</v>
+        <v>2.83</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.23</v>
+        <v>2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.83</v>
+        <v>3.85</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="M2" t="n">
         <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.77</v>
+        <v>2.64</v>
       </c>
       <c r="O2" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
         <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
         <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="T2" t="n">
         <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
         <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45978.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,58 +778,58 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.48</v>
+        <v>1.93</v>
       </c>
       <c r="M3" t="n">
         <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.64</v>
+        <v>3.77</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>4.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
         <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
         <v>1.18</v>
@@ -838,13 +838,13 @@
         <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45978.375</v>
@@ -906,25 +906,25 @@
         <v>2.49</v>
       </c>
       <c r="O4" t="n">
-        <v>5.95</v>
+        <v>5.74</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
         <v>9.1</v>
@@ -948,22 +948,22 @@
         <v>1.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.34</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45978.5</v>
@@ -1025,19 +1025,19 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
         <v>3.5</v>
@@ -1046,7 +1046,7 @@
         <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1055,7 +1055,7 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
         <v>2.49</v>
@@ -1073,16 +1073,16 @@
         <v>1.12</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1147,10 +1147,10 @@
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="R6" t="n">
         <v>1.49</v>
@@ -1159,22 +1159,22 @@
         <v>2.45</v>
       </c>
       <c r="T6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.62</v>
@@ -1186,7 +1186,7 @@
         <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD6" t="n">
         <v>1.18</v>
@@ -1198,10 +1198,10 @@
         <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="M7" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="N7" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.85</v>
+        <v>3.41</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>8.9</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.31</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.58</v>
+        <v>2.95</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.43</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.48</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
         <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>2.64</v>
+        <v>3.77</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>4.67</v>
       </c>
       <c r="R2" t="n">
         <v>1.47</v>
@@ -683,49 +683,49 @@
         <v>2.39</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
         <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB2" t="n">
         <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45978.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="M3" t="n">
         <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.77</v>
+        <v>2.64</v>
       </c>
       <c r="O3" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.67</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
         <v>1.47</v>
@@ -802,49 +802,49 @@
         <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V3" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
         <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB3" t="n">
         <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45978.375</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.23</v>
+        <v>2.48</v>
       </c>
       <c r="M6" t="n">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.81</v>
+        <v>3.41</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.41</v>
+        <v>3.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.22</v>
+        <v>3.23</v>
       </c>
       <c r="M8" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="N8" t="n">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
         <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.88</v>
+        <v>2.81</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -642,39 +642,39 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="O2" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.67</v>
+        <v>3.94</v>
       </c>
       <c r="R2" t="n">
         <v>1.47</v>
@@ -692,22 +692,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC2" t="n">
         <v>4.1</v>
@@ -719,13 +719,13 @@
         <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45978.375</v>
@@ -774,77 +774,77 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="U3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45978.375</v>
@@ -906,34 +906,34 @@
         <v>2.49</v>
       </c>
       <c r="O4" t="n">
-        <v>5.74</v>
+        <v>5.14</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U4" t="n">
         <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
         <v>1.67</v>
@@ -948,22 +948,22 @@
         <v>1.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45978.5</v>
@@ -1025,28 +1025,28 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.35</v>
+        <v>3.19</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1055,10 +1055,10 @@
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
         <v>2.4</v>
@@ -1067,22 +1067,22 @@
         <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.5</v>
+        <v>5.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1144,13 +1144,13 @@
         <v>2.86</v>
       </c>
       <c r="O6" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.41</v>
+        <v>3.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.55</v>
@@ -1159,19 +1159,19 @@
         <v>2.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U6" t="n">
         <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
         <v>1.5</v>
@@ -1186,22 +1186,22 @@
         <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="AD6" t="n">
         <v>1.11</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
         <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1263,40 +1263,40 @@
         <v>3.17</v>
       </c>
       <c r="O7" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
         <v>1.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AA7" t="n">
         <v>2.12</v>
@@ -1305,22 +1305,22 @@
         <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.35</v>
+        <v>3.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1382,40 +1382,40 @@
         <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AA8" t="n">
         <v>2.18</v>
@@ -1424,19 +1424,19 @@
         <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
         <v>1.25</v>

--- a/jogos_2025-11-17.xlsx
+++ b/jogos_2025-11-17.xlsx
@@ -880,45 +880,45 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.19</v>
+        <v>3.91</v>
       </c>
       <c r="M4" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>2.49</v>
+        <v>1.94</v>
       </c>
       <c r="O4" t="n">
-        <v>5.14</v>
+        <v>4.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="T4" t="n">
         <v>3.8</v>
@@ -927,43 +927,43 @@
         <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
         <v>5.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45978.5</v>
@@ -1002,42 +1002,42 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="T5" t="n">
         <v>3.6</v>
@@ -1046,43 +1046,43 @@
         <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.24</v>
+        <v>5.15</v>
       </c>
       <c r="AD5" t="n">
         <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45978.5625</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>2.86</v>
+        <v>3.41</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.95</v>
+        <v>4.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45978.6875</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O7" t="n">
         <v>3.28</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.12</v>
-      </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.1</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45978.6875</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="M8" t="n">
-        <v>3.19</v>
+        <v>2.92</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="O8" t="n">
-        <v>4.35</v>
+        <v>4.16</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
         <v>2.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
         <v>4.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45978.6875</v>
